--- a/docs/dataset/QMRA_Test_Dataset_v2.xlsx
+++ b/docs/dataset/QMRA_Test_Dataset_v2.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L66"/>
+  <dimension ref="A1:L74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -3723,6 +3723,422 @@
       </c>
       <c r="L66" s="8" t="n">
         <v>365</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Pasir Ris Beach</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>15/03/2026</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Water</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Secondary Contact (Kayaking/Wading)</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Escherichia coli</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>UTI</t>
+        </is>
+      </c>
+      <c r="G67" t="n">
+        <v>1200</v>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>CFU/100ml</t>
+        </is>
+      </c>
+      <c r="I67" t="n">
+        <v>85</v>
+      </c>
+      <c r="J67" t="n">
+        <v>0</v>
+      </c>
+      <c r="K67" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="L67" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Pasir Ris Beach</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>15/03/2026</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Water</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Secondary Contact (Kayaking/Wading)</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Escherichia coli</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>BSI</t>
+        </is>
+      </c>
+      <c r="G68" t="n">
+        <v>1200</v>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>CFU/100ml</t>
+        </is>
+      </c>
+      <c r="I68" t="n">
+        <v>85</v>
+      </c>
+      <c r="J68" t="n">
+        <v>0</v>
+      </c>
+      <c r="K68" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="L68" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Pasir Ris Beach</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>15/03/2026</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Water</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Secondary Contact (Kayaking/Wading)</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Escherichia coli</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Gastroenteritis</t>
+        </is>
+      </c>
+      <c r="G69" t="n">
+        <v>1200</v>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>CFU/100ml</t>
+        </is>
+      </c>
+      <c r="I69" t="n">
+        <v>85</v>
+      </c>
+      <c r="J69" t="n">
+        <v>0</v>
+      </c>
+      <c r="K69" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="L69" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Pasir Ris Beach</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>22/03/2026</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Water</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Secondary Contact (Kayaking/Wading)</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Escherichia coli</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>UTI</t>
+        </is>
+      </c>
+      <c r="G70" t="n">
+        <v>450</v>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>CFU/100ml</t>
+        </is>
+      </c>
+      <c r="I70" t="n">
+        <v>32</v>
+      </c>
+      <c r="J70" t="n">
+        <v>0</v>
+      </c>
+      <c r="K70" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="L70" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Pasir Ris Beach</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>22/03/2026</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Water</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Secondary Contact (Kayaking/Wading)</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Escherichia coli</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>BSI</t>
+        </is>
+      </c>
+      <c r="G71" t="n">
+        <v>450</v>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>CFU/100ml</t>
+        </is>
+      </c>
+      <c r="I71" t="n">
+        <v>32</v>
+      </c>
+      <c r="J71" t="n">
+        <v>0</v>
+      </c>
+      <c r="K71" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="L71" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Marina Bay</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Water</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Secondary Contact (Kayaking/Wading)</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Escherichia coli</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>UTI</t>
+        </is>
+      </c>
+      <c r="G72" t="n">
+        <v>2800</v>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>CFU/100ml</t>
+        </is>
+      </c>
+      <c r="I72" t="n">
+        <v>190</v>
+      </c>
+      <c r="J72" t="n">
+        <v>0</v>
+      </c>
+      <c r="K72" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="L72" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Marina Bay</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Water</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Secondary Contact (Kayaking/Wading)</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Escherichia coli</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>BSI</t>
+        </is>
+      </c>
+      <c r="G73" t="n">
+        <v>2800</v>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>CFU/100ml</t>
+        </is>
+      </c>
+      <c r="I73" t="n">
+        <v>190</v>
+      </c>
+      <c r="J73" t="n">
+        <v>0</v>
+      </c>
+      <c r="K73" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="L73" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Marina Bay</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Water</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Secondary Contact (Kayaking/Wading)</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Escherichia coli</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Watery Diarrhea</t>
+        </is>
+      </c>
+      <c r="G74" t="n">
+        <v>980</v>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>CFU/100ml</t>
+        </is>
+      </c>
+      <c r="I74" t="n">
+        <v>60</v>
+      </c>
+      <c r="J74" t="n">
+        <v>0</v>
+      </c>
+      <c r="K74" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="L74" t="n">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
